--- a/quiz/old-quiz/OWO1.1.xlsx
+++ b/quiz/old-quiz/OWO1.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\_5 QUESTION DATABASE\_1 Access Database\OGOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\firebrigade\wp-content\plugins\techiquiz\quiz\old-quiz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2321CE-ACC7-4D57-822C-65F40AE404D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23188CA6-0402-4C66-A317-2724A8EFCCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{05FE482F-9077-4165-BBE2-050B5AFD0DC6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{05FE482F-9077-4165-BBE2-050B5AFD0DC6}"/>
   </bookViews>
   <sheets>
     <sheet name="OWO1" sheetId="1" r:id="rId1"/>
@@ -3528,7 +3528,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -3663,7 +3663,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
